--- a/data/satisfaction_summary/2026/1-6月/1-6月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/1-6月/1-6月客户类型满意度汇总表.xlsx
@@ -586,22 +586,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>9.4</v>
+        <v>9.43</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>9.91</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>8.5</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -642,14 +642,14 @@
         <v>9.99</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>8.84</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -690,16 +690,16 @@
         <v>9.9</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -716,10 +716,10 @@
         <v>9.99</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.23</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.56</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.27</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>9.84</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>9.99</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>9.85</v>
+        <v>9.83</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.69</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
@@ -1138,19 +1138,19 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="4" t="n">
-        <v>9.66</v>
+        <v>9.67</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>9.93</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.48</v>
+        <v>9.49</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>9.609999999999999</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>9.380000000000001</v>
